--- a/docs/importacao/modelos/modelo-funcionarios.xlsx
+++ b/docs/importacao/modelos/modelo-funcionarios.xlsx
@@ -442,7 +442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF2000"/>
+  <dimension ref="A1:AK2000"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -477,6 +477,11 @@
     <col width="18" customWidth="1" min="30" max="30"/>
     <col width="14" customWidth="1" min="31" max="31"/>
     <col width="14" customWidth="1" min="32" max="32"/>
+    <col width="17" customWidth="1" min="33" max="33"/>
+    <col width="15" customWidth="1" min="34" max="34"/>
+    <col width="18" customWidth="1" min="35" max="35"/>
+    <col width="20" customWidth="1" min="36" max="36"/>
+    <col width="17" customWidth="1" min="37" max="37"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -640,6 +645,31 @@
           <t>bolsa_tipo</t>
         </is>
       </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>titulacao_pct</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>anuenio_pct</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>dependentes_ir</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>outros_descontos</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>sindicalizado</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
@@ -741,6 +771,31 @@
       <c r="Z2" s="4" t="n"/>
       <c r="AA2" s="4" t="n"/>
       <c r="AB2" s="3" t="n"/>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -32807,7 +32862,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D35"/>
+  <dimension ref="A1:D40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -33369,8 +33424,98 @@
       </c>
       <c r="D33" t="inlineStr"/>
     </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>titulacao_pct</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr"/>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Adicional de titulação: 0 | 7,5 | 10 | 12,5 (%).</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
     <row r="35">
       <c r="A35" t="inlineStr">
+        <is>
+          <t>anuenio_pct</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr"/>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Anuênio: percentual do salário base (0 a 50).</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>dependentes_ir</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr"/>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Quantidade de dependentes para IR (0 a 20).</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>outros_descontos</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr"/>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Outros descontos fixos mensais (R$).</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>sindicalizado</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr"/>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Paga mensalidade sindical? sim | não.</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
         <is>
           <t>Apague as linhas de exemplo antes de importar. Cabeçalhos em verde são obrigatórios.</t>
         </is>
